--- a/output/pdf_financials_xlsx/SPOT.xlsx
+++ b/output/pdf_financials_xlsx/SPOT.xlsx
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.0075</v>
+        <v>-0.0075</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-1.290805</v>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.0075</v>
+        <v>-0.0075</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-1.290805</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.0075</v>
+        <v>-0.0075</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-1.290805</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.0075</v>
+        <v>-0.0075</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.290805</v>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.0075</v>
+        <v>-0.0075</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.279236</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -28776,10 +28776,10 @@
         </is>
       </c>
       <c r="E395" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0075</v>
       </c>
       <c r="F395" s="5" t="n">
-        <v>0.086781</v>
+        <v>-0.086781</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SPOT.xlsx
+++ b/output/pdf_financials_xlsx/SPOT.xlsx
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.4025</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.640339</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.367966</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.4025</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.640339</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.367966</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.4025</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.643827</v>
+        <v>0.003488</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.9998629999999999</v>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">

--- a/output/pdf_financials_xlsx/SPOT.xlsx
+++ b/output/pdf_financials_xlsx/SPOT.xlsx
@@ -4365,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.002611</v>
       </c>
     </row>
     <row r="113">
@@ -13707,7 +13707,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -19429,7 +19433,11 @@
           <t>Proceeds on sale of property and equipment 13</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SPOT.xlsx
+++ b/output/pdf_financials_xlsx/SPOT.xlsx
@@ -971,13 +971,13 @@
         <v>-1.399246</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.254579</v>
+        <v>0.030342</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>22.830032</v>
+        <v>3.064204</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.06768</v>
+        <v>2.152241</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0.385929</v>
@@ -1105,8 +1105,10 @@
       <c r="D20" s="3" t="n">
         <v>-4.689081</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>1.1e-07</v>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F20" s="3" t="n">
         <v>11.040967</v>
@@ -1140,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-0.074285</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -1531,13 +1533,13 @@
         <v>11.81904415186871</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>11.38227339650286</v>
+        <v>1.356596339040886</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-76.93344720231389</v>
+        <v>-10.32586273427558</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-11.06222162610613</v>
+        <v>-11.51462844095425</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-5.871238312222653</v>
@@ -12660,7 +12662,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -14468,7 +14474,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -15707,7 +15717,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -23214,7 +23228,11 @@
           <t>Income tax recovery 16</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -24217,7 +24235,11 @@
           <t>Income tax recovery 17</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -25370,7 +25392,11 @@
           <t>Income tax recovery 20</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -26826,7 +26852,11 @@
           <t>Net loss from discontinued operations 9</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
